--- a/data/trans_dic/P16A07-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P16A07-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido antidepresivos en las dos últimas semanas</t>
+          <t>Población que ha consumido antidepresivos en las dos últimas semanas (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,1; 4,84</t>
+          <t>1,99; 4,64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,55; 3,97</t>
+          <t>1,53; 4,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,07</t>
+          <t>1,02; 3,16</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,41; 6,75</t>
+          <t>3,47; 6,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,59; 8,02</t>
+          <t>4,38; 8,18</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,62; 12,13</t>
+          <t>7,71; 12,17</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,52; 10,75</t>
+          <t>6,69; 10,93</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,56; 8,26</t>
+          <t>5,47; 8,35</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,61; 5,7</t>
+          <t>3,61; 5,74</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,93; 7,56</t>
+          <t>5,09; 7,73</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,06; 6,54</t>
+          <t>4,09; 6,44</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,84; 6,97</t>
+          <t>4,76; 6,92</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,46; 3,65</t>
+          <t>1,51; 3,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,5; 5,05</t>
+          <t>2,39; 4,98</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,65</t>
+          <t>1,02; 2,63</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,05; 3,2</t>
+          <t>1,01; 3,16</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,13; 8,26</t>
+          <t>5,05; 8,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,39; 10,08</t>
+          <t>6,55; 9,95</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,81; 9,04</t>
+          <t>5,82; 9,05</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,39; 7,71</t>
+          <t>5,47; 7,95</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,55; 5,51</t>
+          <t>3,57; 5,44</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,89; 7,03</t>
+          <t>4,84; 6,99</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,7; 5,53</t>
+          <t>3,71; 5,55</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,54; 4,92</t>
+          <t>2,69; 4,93</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,56</t>
+          <t>0,72; 2,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,1; 3,88</t>
+          <t>1,09; 3,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,22; 3,48</t>
+          <t>1,16; 3,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,09; 4,82</t>
+          <t>2,21; 4,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,98; 7,7</t>
+          <t>4,23; 7,63</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,2; 9,12</t>
+          <t>5,28; 9,31</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,93; 7,31</t>
+          <t>3,97; 7,41</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,23; 9,04</t>
+          <t>3,33; 9,12</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,74; 4,67</t>
+          <t>2,69; 4,67</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,6; 5,94</t>
+          <t>3,63; 5,97</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,82; 4,89</t>
+          <t>2,83; 4,93</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,47; 6,46</t>
+          <t>3,32; 6,45</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,09; 2,77</t>
+          <t>1,08; 2,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,76; 5,75</t>
+          <t>2,64; 5,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,09; 4,35</t>
+          <t>2,07; 4,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,53; 4,77</t>
+          <t>2,59; 4,75</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,7; 8,96</t>
+          <t>5,62; 8,91</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,87; 10,31</t>
+          <t>6,88; 10,37</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,69; 9,05</t>
+          <t>5,68; 9,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,74; 10,14</t>
+          <t>6,64; 10,03</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,73; 5,6</t>
+          <t>3,68; 5,59</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,31; 7,57</t>
+          <t>5,26; 7,56</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,24; 6,36</t>
+          <t>4,32; 6,27</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,34; 7,25</t>
+          <t>5,26; 7,29</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,68; 2,62</t>
+          <t>1,68; 2,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,53; 3,91</t>
+          <t>2,53; 3,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,7; 2,69</t>
+          <t>1,73; 2,74</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,45; 3,92</t>
+          <t>2,47; 3,88</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,63; 7,3</t>
+          <t>5,65; 7,33</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,41; 9,26</t>
+          <t>7,46; 9,34</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,29; 8,0</t>
+          <t>6,23; 8,14</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,76; 7,97</t>
+          <t>5,85; 8,03</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,84; 4,81</t>
+          <t>3,89; 4,8</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5,28; 6,44</t>
+          <t>5,23; 6,44</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4,19; 5,23</t>
+          <t>4,24; 5,27</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,53; 5,82</t>
+          <t>4,55; 5,8</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido antidepresivos en las dos últimas semanas</t>
+          <t>Población que ha consumido antidepresivos en las dos últimas semanas (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>14536; 33552</t>
+          <t>13808; 32141</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10881; 27848</t>
+          <t>10729; 29094</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6529; 20711</t>
+          <t>6879; 21308</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21663; 42884</t>
+          <t>22055; 43288</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>31620; 55216</t>
+          <t>30139; 56316</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>52988; 84340</t>
+          <t>53560; 84617</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>43872; 72340</t>
+          <t>45034; 73523</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>37525; 55772</t>
+          <t>36975; 56402</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>49927; 78707</t>
+          <t>49926; 79264</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>68797; 105588</t>
+          <t>70995; 107857</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>54761; 88079</t>
+          <t>55104; 86750</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>63473; 91388</t>
+          <t>62327; 90678</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14025; 35112</t>
+          <t>14541; 33164</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25494; 51440</t>
+          <t>24320; 50697</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10234; 27066</t>
+          <t>10464; 26873</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12566; 38192</t>
+          <t>12015; 37703</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>49714; 80015</t>
+          <t>48923; 81258</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>65639; 103526</t>
+          <t>67217; 102157</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>60575; 94242</t>
+          <t>60712; 94435</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>51646; 73896</t>
+          <t>52380; 76182</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>68562; 106320</t>
+          <t>68845; 104956</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>100058; 143702</t>
+          <t>99013; 142863</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>76501; 114119</t>
+          <t>76703; 114567</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>54579; 105795</t>
+          <t>57894; 106141</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4963; 17357</t>
+          <t>4872; 16854</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8274; 29332</t>
+          <t>8247; 28074</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9265; 26416</t>
+          <t>8834; 25533</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14708; 33934</t>
+          <t>15521; 35068</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>27205; 52687</t>
+          <t>28956; 52154</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>40403; 70774</t>
+          <t>40979; 72308</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>30834; 57412</t>
+          <t>31150; 58152</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>30140; 84294</t>
+          <t>31075; 85083</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>37290; 63654</t>
+          <t>36611; 63616</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>55107; 90978</t>
+          <t>55592; 91426</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>43634; 75595</t>
+          <t>43784; 76220</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>56754; 105750</t>
+          <t>54283; 105554</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10260; 26057</t>
+          <t>10139; 25731</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>26057; 54281</t>
+          <t>24926; 52906</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>19593; 40806</t>
+          <t>19398; 40854</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>23461; 44176</t>
+          <t>24047; 44002</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>59187; 93091</t>
+          <t>58367; 92572</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>71998; 108100</t>
+          <t>72192; 108782</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>59443; 94412</t>
+          <t>59250; 95609</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>73527; 110669</t>
+          <t>72509; 109459</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>73958; 110903</t>
+          <t>72946; 110724</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>105854; 150864</t>
+          <t>104745; 150736</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>83928; 125948</t>
+          <t>85580; 124274</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>107701; 146366</t>
+          <t>106090; 147207</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>55089; 85755</t>
+          <t>55132; 88484</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>86572; 133555</t>
+          <t>86537; 132995</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>57849; 91412</t>
+          <t>58629; 92928</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>84745; 135474</t>
+          <t>85505; 134337</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>190280; 246748</t>
+          <t>190996; 247695</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>262752; 328478</t>
+          <t>264554; 331394</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>223043; 283410</t>
+          <t>220920; 288598</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>210501; 291456</t>
+          <t>214142; 293572</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>255230; 320257</t>
+          <t>259067; 319516</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>367529; 448340</t>
+          <t>364473; 448511</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>290464; 362774</t>
+          <t>294186; 365908</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>322144; 414280</t>
+          <t>323773; 413007</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A07-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P16A07-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,79%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,99; 4,64</t>
+          <t>1,95; 4,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,53; 4,15</t>
+          <t>1,56; 3,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,02; 3,16</t>
+          <t>1,04; 3,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,47; 6,82</t>
+          <t>3,45; 6,87</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,38; 8,18</t>
+          <t>4,25; 7,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,71; 12,17</t>
+          <t>7,56; 11,93</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,69; 10,93</t>
+          <t>6,53; 10,88</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,47; 8,35</t>
+          <t>5,42; 8,16</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,61; 5,74</t>
+          <t>3,51; 5,67</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,09; 7,73</t>
+          <t>4,92; 7,5</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,09; 6,44</t>
+          <t>4,01; 6,48</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,76; 6,92</t>
+          <t>4,7; 7,01</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,51; 3,45</t>
+          <t>1,45; 3,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,39; 4,98</t>
+          <t>2,48; 5,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,02; 2,63</t>
+          <t>0,99; 2,61</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,01; 3,16</t>
+          <t>1,67; 3,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,05; 8,39</t>
+          <t>5,01; 8,25</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,55; 9,95</t>
+          <t>6,55; 10,06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,82; 9,05</t>
+          <t>5,8; 9,1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,47; 7,95</t>
+          <t>5,25; 7,76</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,57; 5,44</t>
+          <t>3,54; 5,42</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,84; 6,99</t>
+          <t>4,86; 7,04</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,71; 5,55</t>
+          <t>3,65; 5,58</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,69; 4,93</t>
+          <t>3,8; 5,42</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,82%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,48</t>
+          <t>0,71; 2,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,09; 3,72</t>
+          <t>1,08; 3,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,16; 3,36</t>
+          <t>1,23; 3,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,21; 4,98</t>
+          <t>2,32; 4,88</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,23; 7,63</t>
+          <t>4,14; 7,55</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,28; 9,31</t>
+          <t>5,44; 9,24</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,97; 7,41</t>
+          <t>3,98; 7,39</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,33; 9,12</t>
+          <t>6,9; 10,24</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,69; 4,67</t>
+          <t>2,69; 4,71</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,63; 5,97</t>
+          <t>3,76; 5,88</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,83; 4,93</t>
+          <t>2,82; 4,89</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,32; 6,45</t>
+          <t>4,9; 7,03</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,45%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,08; 2,73</t>
+          <t>1,08; 2,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,64; 5,6</t>
+          <t>2,75; 5,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,07; 4,36</t>
+          <t>2,11; 4,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,59; 4,75</t>
+          <t>2,51; 4,61</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,62; 8,91</t>
+          <t>5,56; 8,75</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,88; 10,37</t>
+          <t>6,94; 10,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,68; 9,16</t>
+          <t>5,79; 9,13</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,64; 10,03</t>
+          <t>7,79; 10,48</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,68; 5,59</t>
+          <t>3,74; 5,76</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,26; 7,56</t>
+          <t>5,34; 7,77</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,32; 6,27</t>
+          <t>4,3; 6,4</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,26; 7,29</t>
+          <t>5,54; 7,41</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,62%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,68; 2,7</t>
+          <t>1,68; 2,68</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,53; 3,89</t>
+          <t>2,52; 3,91</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,73; 2,74</t>
+          <t>1,72; 2,77</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,47; 3,88</t>
+          <t>2,85; 4,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,65; 7,33</t>
+          <t>5,64; 7,33</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,46; 9,34</t>
+          <t>7,41; 9,44</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,23; 8,14</t>
+          <t>6,29; 8,08</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,85; 8,03</t>
+          <t>6,95; 8,38</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,89; 4,8</t>
+          <t>3,86; 4,86</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5,23; 6,44</t>
+          <t>5,21; 6,38</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4,24; 5,27</t>
+          <t>4,25; 5,28</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,55; 5,8</t>
+          <t>5,17; 6,12</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30619</t>
+          <t>33577</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>45355</t>
+          <t>48849</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>75974</t>
+          <t>82426</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>13808; 32141</t>
+          <t>13481; 31029</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10729; 29094</t>
+          <t>10902; 27478</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6879; 21308</t>
+          <t>6986; 21828</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22055; 43288</t>
+          <t>23787; 47414</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>30139; 56316</t>
+          <t>29282; 53243</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>53560; 84617</t>
+          <t>52582; 82948</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>45034; 73523</t>
+          <t>43948; 73177</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>36975; 56402</t>
+          <t>39681; 59785</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>49926; 79264</t>
+          <t>48534; 78336</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>70995; 107857</t>
+          <t>68606; 104661</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>55104; 86750</t>
+          <t>54041; 87378</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>62327; 90678</t>
+          <t>66884; 99816</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>24622</t>
+          <t>26756</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>62666</t>
+          <t>69020</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>87287</t>
+          <t>95776</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14541; 33164</t>
+          <t>13948; 32829</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>24320; 50697</t>
+          <t>25258; 51002</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10464; 26873</t>
+          <t>10121; 26675</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12015; 37703</t>
+          <t>17548; 37943</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>48923; 81258</t>
+          <t>48493; 79855</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>67217; 102157</t>
+          <t>67289; 103275</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>60712; 94435</t>
+          <t>60538; 94950</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>52380; 76182</t>
+          <t>56216; 83122</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>68845; 104956</t>
+          <t>68239; 104573</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>99013; 142863</t>
+          <t>99342; 143952</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>76703; 114567</t>
+          <t>75331; 115332</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>57894; 106141</t>
+          <t>80596; 114883</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23382</t>
+          <t>26739</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>61237</t>
+          <t>67242</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>84619</t>
+          <t>93980</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4872; 16854</t>
+          <t>4798; 17446</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8247; 28074</t>
+          <t>8158; 27275</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8834; 25533</t>
+          <t>9311; 26108</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15521; 35068</t>
+          <t>18611; 39171</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>28956; 52154</t>
+          <t>28341; 51624</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>40979; 72308</t>
+          <t>42228; 71730</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>31150; 58152</t>
+          <t>31280; 57977</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>31075; 85083</t>
+          <t>55988; 83116</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>36611; 63616</t>
+          <t>36673; 64126</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>55592; 91426</t>
+          <t>57548; 90125</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>43784; 76220</t>
+          <t>43616; 75603</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>54283; 105554</t>
+          <t>79072; 113495</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>33134</t>
+          <t>34683</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>92939</t>
+          <t>101146</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>126073</t>
+          <t>135828</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10139; 25731</t>
+          <t>10181; 27039</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>24926; 52906</t>
+          <t>25943; 52559</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>19398; 40854</t>
+          <t>19779; 42101</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>24047; 44002</t>
+          <t>24875; 45674</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>58367; 92572</t>
+          <t>57790; 90864</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>72192; 108782</t>
+          <t>72822; 110045</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>59250; 95609</t>
+          <t>60426; 95325</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>72509; 109459</t>
+          <t>87063; 117046</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>72946; 110724</t>
+          <t>74100; 114153</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>104745; 150736</t>
+          <t>106384; 154836</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>85580; 124274</t>
+          <t>85189; 126736</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>106090; 147207</t>
+          <t>116711; 156038</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>111757</t>
+          <t>121754</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>262196</t>
+          <t>286257</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>373953</t>
+          <t>408011</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>55132; 88484</t>
+          <t>54910; 87621</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>86537; 132995</t>
+          <t>86262; 133819</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>58629; 92928</t>
+          <t>58476; 94031</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>85505; 134337</t>
+          <t>100742; 146123</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>190996; 247695</t>
+          <t>190667; 247809</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>264554; 331394</t>
+          <t>262954; 334706</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>220920; 288598</t>
+          <t>223117; 286399</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>214142; 293572</t>
+          <t>259442; 312595</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>259067; 319516</t>
+          <t>256746; 323336</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>364473; 448511</t>
+          <t>362663; 444459</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>294186; 365908</t>
+          <t>294586; 366535</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>323773; 413007</t>
+          <t>375286; 444858</t>
         </is>
       </c>
     </row>
